--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20261025_221413.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20261025_221413.xlsx
@@ -1604,7 +1604,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20261025_221413.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20261025_221413.xlsx
@@ -1604,7 +1604,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
